--- a/results/DR_results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Toxicity/tables/hzd_site_scores.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_TEC_quotient</t>
+          <t>HZD_Toxicity_Percent</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -452,11 +452,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>546.8862872709975</v>
+        <v>100</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -467,11 +467,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>360.6353167654386</v>
+        <v>100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323.051407701296</v>
+        <v>100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2556.139459613995</v>
+        <v>100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -512,11 +512,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>389.1447595169337</v>
+        <v>100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>323.0207538464629</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -542,11 +542,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>965.0597246895593</v>
+        <v>100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -557,11 +557,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>626.3454772460516</v>
+        <v>100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>555.7541358872287</v>
+        <v>100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.2944182421847</v>
+        <v>100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -602,11 +602,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>455.2901281447499</v>
+        <v>100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>367.9311051558853</v>
+        <v>100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>245.1926159538724</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>856.6217823212094</v>
+        <v>100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3855.607461612087</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1149.724994108823</v>
+        <v>100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>207.0579438659458</v>
+        <v>100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2039.584531727344</v>
+        <v>100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -722,11 +722,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>337.3607090928327</v>
+        <v>100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -737,11 +737,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1280.055962132029</v>
+        <v>100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1336.455020765899</v>
+        <v>100</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1260.930648651318</v>
+        <v>100</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -782,11 +782,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>724.5505919915011</v>
+        <v>100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>498.4759345244664</v>
+        <v>100</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>294.0369370837824</v>
+        <v>100</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>291.8593637161068</v>
+        <v>100</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>620.0084421057505</v>
+        <v>100</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -857,11 +857,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>370.5239447808135</v>
+        <v>100</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>360.7196949436424</v>
+        <v>100</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1547.418445218523</v>
+        <v>100</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2444.610007996022</v>
+        <v>100</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -917,11 +917,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>406.5795781388446</v>
+        <v>100</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2022.805759516662</v>
+        <v>100</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -947,11 +947,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>631.9144309478047</v>
+        <v>100</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2844.226360015358</v>
+        <v>100</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1032.145332995505</v>
+        <v>100</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>234.7532068771725</v>
+        <v>100</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>328.1116646398809</v>
+        <v>100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2039.298832631272</v>
+        <v>100</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1037,11 +1037,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2936.464886550528</v>
+        <v>100</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1052,11 +1052,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>404.8127038009187</v>
+        <v>100</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1434.537304015319</v>
+        <v>100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1082,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>480.5934958009264</v>
+        <v>100</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1097,11 +1097,11 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1595.603088504419</v>
+        <v>100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>327.0548948471127</v>
+        <v>100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1127,11 +1127,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2567.921701705455</v>
+        <v>100</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2925.875750432383</v>
+        <v>100</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2686.191880139867</v>
+        <v>100</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1172,11 +1172,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2524.560294320388</v>
+        <v>100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1187,11 +1187,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>683.8857100183628</v>
+        <v>100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3220.618650230261</v>
+        <v>100</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2321.289901301369</v>
+        <v>100</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1232,11 +1232,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>396.6112299329343</v>
+        <v>100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1041.460472141753</v>
+        <v>100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1262,11 +1262,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>259.7106245630908</v>
+        <v>100</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1277,11 +1277,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3618.987219158857</v>
+        <v>100</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>95.30282091625358</v>
+        <v>100</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1307,11 +1307,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1868.516971161154</v>
+        <v>100</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>360.3018697066473</v>
+        <v>100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1131.118265712656</v>
+        <v>100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1352,11 +1352,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>757.2518796502143</v>
+        <v>100</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1367,11 +1367,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>396.6243555823813</v>
+        <v>100</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2427.207442015336</v>
+        <v>100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1397,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1207.542886770313</v>
+        <v>100</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>474.3285163878188</v>
+        <v>100</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024.762538137933</v>
+        <v>100</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1442,11 +1442,11 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>955.5179229718462</v>
+        <v>100</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1457,11 +1457,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>771.5957150011114</v>
+        <v>100</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3219.427834099502</v>
+        <v>100</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2862.402128390998</v>
+        <v>100</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1334.429688323259</v>
+        <v>100</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2015.888612882292</v>
+        <v>100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1033.684920906245</v>
+        <v>100</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1256.055857684058</v>
+        <v>100</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>533.1034047186363</v>
+        <v>100</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1577,11 +1577,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>454.5250660126463</v>
+        <v>100</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1592,11 +1592,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2311.968018222636</v>
+        <v>100</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2808.049236778268</v>
+        <v>100</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1622,11 +1622,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1685.684089901667</v>
+        <v>100</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1180.338209126076</v>
+        <v>100</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1122.274824173758</v>
+        <v>100</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1667,11 +1667,11 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1659.615220500805</v>
+        <v>100</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>496.5426573352681</v>
+        <v>100</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>515.3802232348582</v>
+        <v>100</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1712,11 +1712,11 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>535.0407758200341</v>
+        <v>100</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1727,11 +1727,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2218.983006704507</v>
+        <v>100</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1413.758615588961</v>
+        <v>100</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1757,11 +1757,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2489.46694485589</v>
+        <v>100</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1772,11 +1772,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3824.762156001866</v>
+        <v>100</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1787,11 +1787,11 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>363.8787590418078</v>
+        <v>100</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1802,11 +1802,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>891.0246999633022</v>
+        <v>100</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>370.47640217286</v>
+        <v>100</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1832,11 +1832,11 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>441.6795858714871</v>
+        <v>100</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>987.6297528963544</v>
+        <v>100</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>283.2726392272232</v>
+        <v>100</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1877,11 +1877,11 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>381.4001161546993</v>
+        <v>100</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>373.1704849866163</v>
+        <v>100</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1907,11 +1907,11 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>875.5709275513107</v>
+        <v>100</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1358.858232890638</v>
+        <v>100</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1937,11 +1937,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>181.1997641153565</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3179.781182840011</v>
+        <v>100</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3142.640102524054</v>
+        <v>100</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1982,11 +1982,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>441.136470741838</v>
+        <v>100</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1039.188751641183</v>
+        <v>100</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2012,11 +2012,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>963.859908813514</v>
+        <v>100</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>910.127316173354</v>
+        <v>100</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2042,11 +2042,11 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>428.0664505928089</v>
+        <v>100</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2694.184434639124</v>
+        <v>100</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2072,11 +2072,11 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2003.593883557836</v>
+        <v>100</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>169.9943731212041</v>
+        <v>100</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>515.9467661722379</v>
+        <v>100</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2117,11 +2117,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>250.7853030719525</v>
+        <v>100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2132,11 +2132,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>583.505704203978</v>
+        <v>100</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2147,11 +2147,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>311.7563898753855</v>
+        <v>100</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>198.2376242625456</v>
+        <v>100</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2177,11 +2177,11 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>513.1136162930709</v>
+        <v>100</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2192,11 +2192,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>336.9837854810057</v>
+        <v>100</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2207,11 +2207,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>496.7402313037054</v>
+        <v>100</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>336.3256766938426</v>
+        <v>100</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2237,11 +2237,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>793.5918378849225</v>
+        <v>100</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2252,11 +2252,11 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>255.8564348346725</v>
+        <v>100</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2267,11 +2267,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>343.7205495724889</v>
+        <v>100</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2282,11 +2282,11 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>296.5898617084659</v>
+        <v>100</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2297,11 +2297,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>401.0753779079404</v>
+        <v>100</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2312,11 +2312,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2031.289738977498</v>
+        <v>100</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2327,11 +2327,11 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>351.1248217609392</v>
+        <v>100</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2342,11 +2342,11 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1095.356525225187</v>
+        <v>100</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2357,11 +2357,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>394.6835944254109</v>
+        <v>100</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5205546767190856</v>
+        <v>0</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2387,11 +2387,11 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.2270161697541991</v>
+        <v>0</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2402,11 +2402,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.1825130642224894</v>
+        <v>0</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1130597803117607</v>
+        <v>0</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2432,11 +2432,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.1834459944775769</v>
+        <v>0</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2447,11 +2447,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.7470427322152114</v>
+        <v>34.23421327856809</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2462,11 +2462,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.7295156377576173</v>
+        <v>24.58928343490263</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5.384312685924876</v>
+        <v>100</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2492,11 +2492,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5130559324059444</v>
+        <v>5.327838802008446</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.084657664641707</v>
+        <v>40.97335249778372</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2522,11 +2522,11 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2.427564381354639</v>
+        <v>100</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2537,11 +2537,11 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.559125160484891</v>
+        <v>20.99222465691347</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2552,11 +2552,11 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.7207287762010216</v>
+        <v>22.25386589281224</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2567,11 +2567,11 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.3900247357395382</v>
+        <v>5.091373116196439</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.1897280823443891</v>
+        <v>0</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2597,11 +2597,11 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.36626348840349</v>
+        <v>0</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Zero</t>
         </is>
       </c>
     </row>
@@ -2612,11 +2612,11 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1.424195694697974</v>
+        <v>92.98775109907241</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Above PEC</t>
         </is>
       </c>
     </row>
@@ -2627,11 +2627,11 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.3474352783346483</v>
+        <v>5.405775384698827</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>TEC-PEC</t>
         </is>
       </c>
     </row>
